--- a/Employee_Reports_wi52/Ericson Murcillos Victorino Q0068.xlsx
+++ b/Employee_Reports_wi52/Ericson Murcillos Victorino Q0068.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-253</v>
+        <v>-261</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -655,11 +655,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-387</v>
+        <v>-395</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -729,11 +729,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -766,11 +766,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
